--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -1157,8 +1157,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G373"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="10" customWidth="1"/>
@@ -1330,395 +1330,6 @@
       <c r="F8" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" s="12"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" s="6" customFormat="1" spans="2:6">
-      <c r="B10" s="12"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" s="6" customFormat="1"/>
-    <row r="12" s="6" customFormat="1"/>
-    <row r="13" s="6" customFormat="1"/>
-    <row r="14" s="6" customFormat="1"/>
-    <row r="15" s="6" customFormat="1"/>
-    <row r="16" s="6" customFormat="1"/>
-    <row r="17" s="6" customFormat="1"/>
-    <row r="18" s="6" customFormat="1"/>
-    <row r="19" s="6" customFormat="1"/>
-    <row r="20" s="6" customFormat="1"/>
-    <row r="21" s="6" customFormat="1"/>
-    <row r="22" s="6" customFormat="1"/>
-    <row r="23" s="6" customFormat="1"/>
-    <row r="24" s="6" customFormat="1"/>
-    <row r="25" s="6" customFormat="1"/>
-    <row r="26" s="6" customFormat="1"/>
-    <row r="27" s="6" customFormat="1"/>
-    <row r="28" s="6" customFormat="1"/>
-    <row r="29" s="6" customFormat="1"/>
-    <row r="30" s="6" customFormat="1"/>
-    <row r="31" s="6" customFormat="1"/>
-    <row r="32" s="6" customFormat="1"/>
-    <row r="33" s="6" customFormat="1"/>
-    <row r="34" s="6" customFormat="1"/>
-    <row r="35" s="6" customFormat="1"/>
-    <row r="36" s="6" customFormat="1"/>
-    <row r="37" s="6" customFormat="1"/>
-    <row r="38" s="6" customFormat="1"/>
-    <row r="39" s="6" customFormat="1"/>
-    <row r="40" s="6" customFormat="1"/>
-    <row r="41" s="6" customFormat="1"/>
-    <row r="42" s="6" customFormat="1"/>
-    <row r="43" s="6" customFormat="1"/>
-    <row r="44" s="6" customFormat="1"/>
-    <row r="45" s="6" customFormat="1"/>
-    <row r="46" s="6" customFormat="1"/>
-    <row r="47" s="6" customFormat="1"/>
-    <row r="48" s="6" customFormat="1"/>
-    <row r="49" s="6" customFormat="1"/>
-    <row r="50" s="6" customFormat="1"/>
-    <row r="51" s="6" customFormat="1"/>
-    <row r="52" s="6" customFormat="1"/>
-    <row r="53" s="6" customFormat="1"/>
-    <row r="54" s="6" customFormat="1"/>
-    <row r="55" s="6" customFormat="1"/>
-    <row r="56" s="6" customFormat="1"/>
-    <row r="57" s="6" customFormat="1"/>
-    <row r="58" s="6" customFormat="1"/>
-    <row r="59" s="6" customFormat="1"/>
-    <row r="60" s="6" customFormat="1"/>
-    <row r="61" s="6" customFormat="1"/>
-    <row r="62" s="6" customFormat="1"/>
-    <row r="63" s="6" customFormat="1"/>
-    <row r="64" s="6" customFormat="1"/>
-    <row r="65" s="6" customFormat="1"/>
-    <row r="66" s="6" customFormat="1"/>
-    <row r="67" s="6" customFormat="1"/>
-    <row r="68" s="6" customFormat="1"/>
-    <row r="69" s="6" customFormat="1"/>
-    <row r="70" s="6" customFormat="1"/>
-    <row r="71" s="6" customFormat="1"/>
-    <row r="72" s="6" customFormat="1"/>
-    <row r="73" s="6" customFormat="1"/>
-    <row r="74" s="6" customFormat="1"/>
-    <row r="75" s="6" customFormat="1"/>
-    <row r="76" s="6" customFormat="1"/>
-    <row r="77" s="6" customFormat="1"/>
-    <row r="78" s="6" customFormat="1"/>
-    <row r="79" s="6" customFormat="1"/>
-    <row r="80" s="6" customFormat="1"/>
-    <row r="81" s="6" customFormat="1"/>
-    <row r="82" s="6" customFormat="1"/>
-    <row r="83" s="6" customFormat="1"/>
-    <row r="84" s="6" customFormat="1"/>
-    <row r="85" s="6" customFormat="1"/>
-    <row r="86" s="6" customFormat="1"/>
-    <row r="87" s="6" customFormat="1"/>
-    <row r="88" s="6" customFormat="1"/>
-    <row r="89" s="6" customFormat="1"/>
-    <row r="90" s="6" customFormat="1"/>
-    <row r="91" s="6" customFormat="1"/>
-    <row r="92" s="6" customFormat="1"/>
-    <row r="93" s="6" customFormat="1"/>
-    <row r="94" s="6" customFormat="1"/>
-    <row r="95" s="6" customFormat="1"/>
-    <row r="96" s="6" customFormat="1"/>
-    <row r="97" s="6" customFormat="1"/>
-    <row r="98" s="6" customFormat="1"/>
-    <row r="99" s="6" customFormat="1"/>
-    <row r="100" s="6" customFormat="1"/>
-    <row r="101" s="6" customFormat="1"/>
-    <row r="102" s="6" customFormat="1"/>
-    <row r="103" s="6" customFormat="1"/>
-    <row r="104" s="6" customFormat="1"/>
-    <row r="105" s="6" customFormat="1"/>
-    <row r="106" s="6" customFormat="1"/>
-    <row r="107" s="6" customFormat="1"/>
-    <row r="108" s="6" customFormat="1"/>
-    <row r="109" s="6" customFormat="1"/>
-    <row r="110" s="6" customFormat="1"/>
-    <row r="111" s="6" customFormat="1"/>
-    <row r="112" s="6" customFormat="1"/>
-    <row r="113" s="6" customFormat="1"/>
-    <row r="114" s="6" customFormat="1"/>
-    <row r="115" s="6" customFormat="1"/>
-    <row r="116" s="6" customFormat="1"/>
-    <row r="117" s="6" customFormat="1"/>
-    <row r="118" s="6" customFormat="1"/>
-    <row r="119" s="6" customFormat="1"/>
-    <row r="120" s="6" customFormat="1"/>
-    <row r="121" s="6" customFormat="1"/>
-    <row r="122" s="6" customFormat="1"/>
-    <row r="123" s="6" customFormat="1"/>
-    <row r="124" s="6" customFormat="1"/>
-    <row r="125" s="6" customFormat="1"/>
-    <row r="126" s="6" customFormat="1"/>
-    <row r="127" s="6" customFormat="1"/>
-    <row r="128" s="6" customFormat="1"/>
-    <row r="129" s="6" customFormat="1"/>
-    <row r="130" s="6" customFormat="1"/>
-    <row r="131" s="6" customFormat="1"/>
-    <row r="132" s="6" customFormat="1"/>
-    <row r="133" s="6" customFormat="1"/>
-    <row r="134" s="6" customFormat="1"/>
-    <row r="135" s="6" customFormat="1"/>
-    <row r="136" s="6" customFormat="1"/>
-    <row r="137" s="6" customFormat="1"/>
-    <row r="138" s="6" customFormat="1"/>
-    <row r="139" s="6" customFormat="1"/>
-    <row r="140" s="6" customFormat="1"/>
-    <row r="141" s="6" customFormat="1"/>
-    <row r="142" s="6" customFormat="1"/>
-    <row r="143" s="6" customFormat="1"/>
-    <row r="144" s="6" customFormat="1"/>
-    <row r="145" s="6" customFormat="1"/>
-    <row r="146" s="6" customFormat="1"/>
-    <row r="147" s="6" customFormat="1"/>
-    <row r="148" s="6" customFormat="1"/>
-    <row r="149" s="6" customFormat="1"/>
-    <row r="150" s="6" customFormat="1"/>
-    <row r="151" s="6" customFormat="1"/>
-    <row r="152" s="6" customFormat="1"/>
-    <row r="153" s="6" customFormat="1"/>
-    <row r="154" s="6" customFormat="1"/>
-    <row r="155" s="6" customFormat="1"/>
-    <row r="156" s="6" customFormat="1"/>
-    <row r="157" s="6" customFormat="1"/>
-    <row r="158" s="6" customFormat="1"/>
-    <row r="159" s="6" customFormat="1"/>
-    <row r="160" s="6" customFormat="1"/>
-    <row r="161" s="6" customFormat="1"/>
-    <row r="162" s="6" customFormat="1"/>
-    <row r="163" s="6" customFormat="1"/>
-    <row r="164" s="6" customFormat="1"/>
-    <row r="165" s="6" customFormat="1"/>
-    <row r="166" s="6" customFormat="1"/>
-    <row r="167" s="6" customFormat="1"/>
-    <row r="168" s="6" customFormat="1"/>
-    <row r="169" s="6" customFormat="1"/>
-    <row r="170" s="6" customFormat="1"/>
-    <row r="171" s="6" customFormat="1"/>
-    <row r="172" s="6" customFormat="1"/>
-    <row r="173" s="6" customFormat="1"/>
-    <row r="174" s="6" customFormat="1"/>
-    <row r="175" s="6" customFormat="1"/>
-    <row r="176" s="6" customFormat="1"/>
-    <row r="177" s="6" customFormat="1"/>
-    <row r="178" s="6" customFormat="1"/>
-    <row r="179" s="6" customFormat="1"/>
-    <row r="180" s="6" customFormat="1"/>
-    <row r="181" s="6" customFormat="1"/>
-    <row r="182" s="6" customFormat="1"/>
-    <row r="183" s="6" customFormat="1"/>
-    <row r="184" s="6" customFormat="1"/>
-    <row r="185" s="6" customFormat="1"/>
-    <row r="186" s="6" customFormat="1"/>
-    <row r="187" s="6" customFormat="1"/>
-    <row r="188" s="6" customFormat="1"/>
-    <row r="189" s="6" customFormat="1"/>
-    <row r="190" s="6" customFormat="1"/>
-    <row r="191" s="6" customFormat="1"/>
-    <row r="192" s="6" customFormat="1"/>
-    <row r="193" s="6" customFormat="1"/>
-    <row r="194" s="6" customFormat="1"/>
-    <row r="195" s="6" customFormat="1"/>
-    <row r="196" s="6" customFormat="1"/>
-    <row r="197" s="6" customFormat="1"/>
-    <row r="198" s="6" customFormat="1"/>
-    <row r="199" s="6" customFormat="1"/>
-    <row r="200" s="6" customFormat="1"/>
-    <row r="201" s="6" customFormat="1"/>
-    <row r="202" s="6" customFormat="1"/>
-    <row r="203" s="6" customFormat="1"/>
-    <row r="204" s="6" customFormat="1"/>
-    <row r="205" s="6" customFormat="1"/>
-    <row r="206" s="6" customFormat="1"/>
-    <row r="207" s="6" customFormat="1"/>
-    <row r="208" s="6" customFormat="1"/>
-    <row r="209" s="6" customFormat="1"/>
-    <row r="210" s="6" customFormat="1"/>
-    <row r="211" s="6" customFormat="1"/>
-    <row r="212" s="6" customFormat="1"/>
-    <row r="213" s="6" customFormat="1"/>
-    <row r="214" s="6" customFormat="1"/>
-    <row r="215" s="6" customFormat="1"/>
-    <row r="216" s="6" customFormat="1"/>
-    <row r="217" s="6" customFormat="1"/>
-    <row r="218" s="6" customFormat="1"/>
-    <row r="219" s="6" customFormat="1"/>
-    <row r="220" s="6" customFormat="1"/>
-    <row r="221" s="6" customFormat="1"/>
-    <row r="222" s="6" customFormat="1"/>
-    <row r="223" s="6" customFormat="1"/>
-    <row r="224" s="6" customFormat="1"/>
-    <row r="225" s="6" customFormat="1"/>
-    <row r="226" s="6" customFormat="1"/>
-    <row r="227" s="6" customFormat="1"/>
-    <row r="228" s="6" customFormat="1"/>
-    <row r="229" s="6" customFormat="1"/>
-    <row r="230" s="6" customFormat="1"/>
-    <row r="231" s="6" customFormat="1"/>
-    <row r="232" s="6" customFormat="1"/>
-    <row r="233" s="6" customFormat="1"/>
-    <row r="234" s="6" customFormat="1"/>
-    <row r="235" s="6" customFormat="1"/>
-    <row r="236" s="6" customFormat="1"/>
-    <row r="237" s="6" customFormat="1"/>
-    <row r="238" s="6" customFormat="1"/>
-    <row r="239" s="6" customFormat="1"/>
-    <row r="240" s="6" customFormat="1"/>
-    <row r="241" s="6" customFormat="1"/>
-    <row r="242" s="6" customFormat="1"/>
-    <row r="243" s="6" customFormat="1"/>
-    <row r="244" s="6" customFormat="1"/>
-    <row r="245" s="6" customFormat="1"/>
-    <row r="246" s="6" customFormat="1"/>
-    <row r="247" s="6" customFormat="1"/>
-    <row r="248" s="6" customFormat="1"/>
-    <row r="249" s="6" customFormat="1"/>
-    <row r="250" s="6" customFormat="1"/>
-    <row r="251" s="6" customFormat="1"/>
-    <row r="252" s="6" customFormat="1"/>
-    <row r="253" s="6" customFormat="1"/>
-    <row r="254" s="6" customFormat="1"/>
-    <row r="255" s="6" customFormat="1"/>
-    <row r="256" s="6" customFormat="1"/>
-    <row r="257" s="6" customFormat="1"/>
-    <row r="258" s="6" customFormat="1"/>
-    <row r="259" s="6" customFormat="1"/>
-    <row r="260" s="6" customFormat="1"/>
-    <row r="261" s="6" customFormat="1"/>
-    <row r="262" s="6" customFormat="1"/>
-    <row r="263" s="6" customFormat="1"/>
-    <row r="264" s="6" customFormat="1"/>
-    <row r="265" s="6" customFormat="1"/>
-    <row r="266" s="6" customFormat="1"/>
-    <row r="267" s="6" customFormat="1"/>
-    <row r="268" s="6" customFormat="1"/>
-    <row r="269" s="6" customFormat="1"/>
-    <row r="270" s="6" customFormat="1"/>
-    <row r="271" s="6" customFormat="1"/>
-    <row r="272" s="6" customFormat="1"/>
-    <row r="273" s="6" customFormat="1"/>
-    <row r="274" s="6" customFormat="1"/>
-    <row r="275" s="6" customFormat="1"/>
-    <row r="276" s="6" customFormat="1"/>
-    <row r="277" s="6" customFormat="1"/>
-    <row r="278" s="6" customFormat="1"/>
-    <row r="279" s="6" customFormat="1"/>
-    <row r="280" s="6" customFormat="1"/>
-    <row r="281" s="6" customFormat="1"/>
-    <row r="282" s="6" customFormat="1"/>
-    <row r="283" s="6" customFormat="1"/>
-    <row r="284" s="6" customFormat="1"/>
-    <row r="285" s="6" customFormat="1"/>
-    <row r="286" s="6" customFormat="1"/>
-    <row r="287" s="6" customFormat="1"/>
-    <row r="288" s="6" customFormat="1"/>
-    <row r="289" s="6" customFormat="1"/>
-    <row r="290" s="6" customFormat="1"/>
-    <row r="291" s="6" customFormat="1"/>
-    <row r="292" s="6" customFormat="1"/>
-    <row r="293" s="6" customFormat="1"/>
-    <row r="294" s="6" customFormat="1"/>
-    <row r="295" s="6" customFormat="1"/>
-    <row r="296" s="6" customFormat="1"/>
-    <row r="297" s="6" customFormat="1"/>
-    <row r="298" s="6" customFormat="1"/>
-    <row r="299" s="6" customFormat="1"/>
-    <row r="300" s="6" customFormat="1"/>
-    <row r="301" s="6" customFormat="1"/>
-    <row r="302" s="6" customFormat="1"/>
-    <row r="303" s="6" customFormat="1"/>
-    <row r="304" s="6" customFormat="1"/>
-    <row r="305" s="6" customFormat="1"/>
-    <row r="306" s="6" customFormat="1"/>
-    <row r="307" s="6" customFormat="1"/>
-    <row r="308" s="6" customFormat="1"/>
-    <row r="309" s="6" customFormat="1"/>
-    <row r="310" s="6" customFormat="1"/>
-    <row r="311" s="6" customFormat="1"/>
-    <row r="312" s="6" customFormat="1"/>
-    <row r="313" s="6" customFormat="1"/>
-    <row r="314" s="6" customFormat="1"/>
-    <row r="315" s="6" customFormat="1"/>
-    <row r="316" s="6" customFormat="1"/>
-    <row r="317" s="6" customFormat="1"/>
-    <row r="318" s="6" customFormat="1"/>
-    <row r="319" s="6" customFormat="1"/>
-    <row r="320" s="6" customFormat="1"/>
-    <row r="321" s="6" customFormat="1"/>
-    <row r="322" s="6" customFormat="1"/>
-    <row r="323" s="6" customFormat="1"/>
-    <row r="324" s="6" customFormat="1"/>
-    <row r="325" s="6" customFormat="1"/>
-    <row r="326" s="6" customFormat="1"/>
-    <row r="327" s="6" customFormat="1"/>
-    <row r="328" s="6" customFormat="1"/>
-    <row r="329" s="6" customFormat="1"/>
-    <row r="330" s="6" customFormat="1"/>
-    <row r="331" s="6" customFormat="1"/>
-    <row r="332" s="6" customFormat="1"/>
-    <row r="333" s="6" customFormat="1"/>
-    <row r="334" s="6" customFormat="1"/>
-    <row r="335" s="6" customFormat="1"/>
-    <row r="336" s="6" customFormat="1"/>
-    <row r="337" s="6" customFormat="1"/>
-    <row r="338" s="6" customFormat="1"/>
-    <row r="339" s="6" customFormat="1"/>
-    <row r="340" s="6" customFormat="1"/>
-    <row r="341" s="6" customFormat="1"/>
-    <row r="342" s="6" customFormat="1"/>
-    <row r="343" s="6" customFormat="1"/>
-    <row r="344" s="6" customFormat="1"/>
-    <row r="345" s="6" customFormat="1"/>
-    <row r="346" s="6" customFormat="1"/>
-    <row r="347" s="6" customFormat="1"/>
-    <row r="348" s="6" customFormat="1"/>
-    <row r="349" s="6" customFormat="1"/>
-    <row r="350" s="6" customFormat="1"/>
-    <row r="351" s="6" customFormat="1"/>
-    <row r="352" s="6" customFormat="1"/>
-    <row r="353" s="6" customFormat="1"/>
-    <row r="354" s="6" customFormat="1"/>
-    <row r="355" s="6" customFormat="1"/>
-    <row r="356" s="6" customFormat="1"/>
-    <row r="357" s="6" customFormat="1"/>
-    <row r="358" s="6" customFormat="1"/>
-    <row r="359" s="6" customFormat="1"/>
-    <row r="360" s="6" customFormat="1"/>
-    <row r="361" s="6" customFormat="1"/>
-    <row r="362" s="6" customFormat="1"/>
-    <row r="363" s="6" customFormat="1"/>
-    <row r="364" s="6" customFormat="1"/>
-    <row r="365" s="6" customFormat="1"/>
-    <row r="366" s="6" customFormat="1"/>
-    <row r="367" s="6" customFormat="1"/>
-    <row r="368" s="6" customFormat="1"/>
-    <row r="369" s="6" customFormat="1"/>
-    <row r="370" s="6" customFormat="1"/>
-    <row r="371" s="6" customFormat="1"/>
-    <row r="372" s="6" customFormat="1" spans="2:7">
-      <c r="B372" s="10"/>
-      <c r="C372" s="9"/>
-      <c r="D372" s="9"/>
-      <c r="E372" s="9"/>
-      <c r="F372" s="9"/>
-      <c r="G372" s="9"/>
-    </row>
-    <row r="373" s="6" customFormat="1" spans="2:7">
-      <c r="B373" s="10"/>
-      <c r="C373" s="9"/>
-      <c r="D373" s="9"/>
-      <c r="E373" s="9"/>
-      <c r="F373" s="9"/>
-      <c r="G373" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Map101</t>
+  </si>
+  <si>
+    <t>Mail</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1157,8 +1160,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="10" customWidth="1"/>
@@ -1329,6 +1332,23 @@
       </c>
       <c r="F8" s="9" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="10">
+        <v>114</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1429,10 +1449,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1449,10 +1469,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1574,10 +1594,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1714,10 +1734,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1735,10 +1755,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1756,10 +1776,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1777,10 +1797,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1798,10 +1818,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Mail</t>
+  </si>
+  <si>
+    <t>Chat</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1160,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1349,6 +1352,23 @@
       </c>
       <c r="F9" s="9" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="10">
+        <v>115</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1449,10 +1469,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1594,10 +1614,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1734,10 +1754,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1755,10 +1775,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1776,10 +1796,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1797,10 +1817,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1818,10 +1838,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Chat</t>
+  </si>
+  <si>
+    <t>Friend</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1163,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1369,6 +1372,23 @@
       </c>
       <c r="F10" s="9" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="10">
+        <v>116</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1614,10 +1634,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1754,10 +1774,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1775,10 +1795,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1796,10 +1816,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1817,10 +1837,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1838,10 +1858,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Friend</t>
+  </si>
+  <si>
+    <t>Center</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1166,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1389,6 +1392,23 @@
       </c>
       <c r="F11" s="9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="10">
+        <v>117</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1634,10 +1654,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1774,10 +1794,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1795,10 +1815,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1816,10 +1836,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1837,10 +1857,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1858,10 +1878,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Center</t>
+  </si>
+  <si>
+    <t>Rank</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1169,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1409,6 +1412,23 @@
       </c>
       <c r="F12" s="9" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="10">
+        <v>118</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1549,10 +1569,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1654,10 +1674,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1794,10 +1814,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1815,10 +1835,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1836,10 +1856,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1857,10 +1877,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1878,10 +1898,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Rank</t>
+  </si>
+  <si>
+    <t>Alliance</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1172,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1429,6 +1432,23 @@
       </c>
       <c r="F13" s="9" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="10">
+        <v>119</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1549,10 +1569,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1569,10 +1589,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1674,10 +1694,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1814,10 +1834,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1835,10 +1855,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1856,10 +1876,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1877,10 +1897,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1898,10 +1918,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>
